--- a/sources/gunjack_step6b.xlsx
+++ b/sources/gunjack_step6b.xlsx
@@ -6333,7 +6333,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q110" t="inlineStr">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">

--- a/sources/gunjack_step6b.xlsx
+++ b/sources/gunjack_step6b.xlsx
@@ -1176,6 +1176,11 @@
           <t>The initial grab does no damage.</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>ebd747c4-4a3a-4cb9-96c6-6ce86ed0ce58</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>ebd747c4-4a3a-4cb9-96c6-6ce86ed0ce58</t>
@@ -1218,6 +1223,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>e5ab66b0-1617-4024-933b-69248c5a2646</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>e5ab66b0-1617-4024-933b-69248c5a2646</t>
@@ -1275,6 +1285,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>48ad3fb6-8248-4bd4-b552-f8a579f06b84</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr">
         <is>
           <t>48ad3fb6-8248-4bd4-b552-f8a579f06b84</t>
@@ -1322,6 +1337,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>dc329630-4a74-4808-906f-cc4361fed63a</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
           <t>dc329630-4a74-4808-906f-cc4361fed63a</t>
@@ -1369,6 +1389,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>b792ea67-ccd8-406a-8717-ceff6184d4ad</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr">
         <is>
           <t>b792ea67-ccd8-406a-8717-ceff6184d4ad</t>
@@ -1409,6 +1434,11 @@
       <c r="M20" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>251f1e2f-c3c7-4333-a3d4-49d19c52d36c</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -6723,6 +6753,11 @@
           <t>sLLmmmmmmm</t>
         </is>
       </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>e5ff6ee8-5845-40b6-9808-a462283cbb8e</t>
+        </is>
+      </c>
       <c r="R118" t="inlineStr">
         <is>
           <t>e5ff6ee8-5845-40b6-9808-a462283cbb8e</t>
@@ -6755,6 +6790,11 @@
           <t>sLLmmmmmlm</t>
         </is>
       </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>1f5e0257-77a7-446c-bec0-1c07fa3d43ff</t>
+        </is>
+      </c>
       <c r="R119" t="inlineStr">
         <is>
           <t>1f5e0257-77a7-446c-bec0-1c07fa3d43ff</t>
@@ -6787,6 +6827,11 @@
           <t>hmLLLmmmmm</t>
         </is>
       </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>59ea3718-6755-453f-bde7-fd7f8178bb67</t>
+        </is>
+      </c>
       <c r="R120" t="inlineStr">
         <is>
           <t>59ea3718-6755-453f-bde7-fd7f8178bb67</t>
@@ -6817,6 +6862,11 @@
       <c r="K121" t="inlineStr">
         <is>
           <t>hmLLLmmmlm</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>2fc42861-9255-4a82-8966-00993ca4d00e</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">

--- a/sources/gunjack_step6b.xlsx
+++ b/sources/gunjack_step6b.xlsx
@@ -3394,7 +3394,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Df+1,2,1</t>
+          <t>DF,1,2,1</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3652,7 +3652,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Df+1,2</t>
+          <t>DF,1,2</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Df+1+2</t>
+          <t>DF,1+2</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4939,7 +4939,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Df+2</t>
+          <t>DF,2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5249,7 +5249,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Df+2,1,2</t>
+          <t>DF,2,1,2</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5946,6 +5946,11 @@
           <t>– 1,2,1,2</t>
         </is>
       </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
+        </is>
+      </c>
       <c r="C101" t="inlineStr">
         <is>
           <t>– Sitting Punches</t>
@@ -6063,6 +6068,11 @@
       <c r="A103" t="inlineStr">
         <is>
           <t>– 1,2,1,2</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2,1,2,1</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
